--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.1-2026-07-06.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.1-2026-07-06.xlsx
@@ -12941,7 +12941,7 @@
 |  Why this order?  &gt;          |
 |                              |
 |  With your order:            |
-|   Will it last   84% -&gt; 82%  |
+|   Will my money last   84% -&gt; 82%  |
 |   Lasts to age    92 -&gt; 90   |
 |   (estimates)                |
 |                              |
@@ -13058,7 +13058,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>'With your order: Will it last 84% → 82%, lasts to age 92 → 90 (estimates)' — suggested versus user order, side by side, before committing.</t>
+          <t>'With your order: Will my money last 84% → 82%, lasts to age 92 → 90 (estimates)' — suggested versus user order, side by side, before committing.</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.1-2026-07-06.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.1-2026-07-06.xlsx
@@ -5187,13 +5187,7 @@
 Screen reader order: greeting → hero as ONE sentence ('Your investments: 843,700 dollars, up 11,200 dollars this month, ahead of the market by half a percent, prices as of 4 pm') → each attention item as one sentence → will-it-last ('Likely, 84 percent, estimate. Opens Plan.'). Eye toggle announces 'Hide balances'/'Show balances' (pattern already in src/components/TopBar.tsx). All rows and buttons at least 44 points tall. Direction always word+arrow, never color alone. Hero number scales down via compact style (e.g. $842.3k) under large-type settings rather than truncating.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>"up $11,200 this month Triangle up" should be "Triangle (green color) up $11,200 this month"
-"Will it Last?" Is not clear if this is regarding retirement, and will it last till what age? 
-And info dots for investments, market, Net Worth.</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5302,11 +5296,7 @@
           <t>Must equal the Invest tab header total and the 'Investments' section of the Net worth tab, to the dollar</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Investment = stock + etfs + bonds + alternatives? It does not include cash or cash equivalents - Right?</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -5361,11 +5351,7 @@
           <t>Must equal the versus-market line on the Performance screen for the same period</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Benchmark in S&amp;P 500? If that add info dot</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -5739,11 +5725,7 @@
 Hero reads as one sentence: 'Safe to spend in July: 5,840 dollars, an estimate. 4,200 guaranteed from Social Security and pension, 1,640 safe to draw from savings. About 71,600 dollars this year.' Worth-a-look card announces 'Worth a look' first, then the fact — screen-reader tone matches visual calm. Larger default type for this lens (retiree eyes); all targets ≥44pt; breakdown uses tree lines PLUS the words Guaranteed/Safe draw, never indentation alone.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Re-evaluate the order of wordings - e.g. "Guaranteed $4200 Social Security + Pension" Norm is Social Security + Pension $4200 (Guaranteed) particularly with pay check but do your research. If it is suppose to be "Guaranteed Social Security $4200" That's perfect.</t>
-        </is>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24" ht="46" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -5825,11 +5807,7 @@
           <t>PIN: guaranteed + safe draw − big bills landing this month = the this-month figure to the dollar, on Home AND Cash flow (agreement test). The bills line appears on Home whenever it is non-zero — the card must visibly sum in every month.</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>What if safe draw is less the big bill. Where will that information be available?</t>
-        </is>
-      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -6171,11 +6149,7 @@
           <t>The 'usual amount' shown here is the exact figure the rule used — stored on the flag at flag time, so the explanation never drifts from the decision</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>How are response formulated? Are we using LLM or theseare pre-crafted responses and app uses one the pre-crafted response just replacing $$$?</t>
-        </is>
-      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40" ht="46" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -6345,11 +6319,7 @@
 Radio groups with full labels; the consequence sentence ('this sets up your Home and tab order') is read before the choices. Large targets; no time pressure.</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>What did yo u come for? - we should specifiy they can select multiple options as retired person can still ne interested in growing her investments or see everything in one place. (2) When person first download Finwise - should we tell user what Finwise can do?</t>
-        </is>
-      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47" ht="46" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -6431,11 +6401,7 @@
           <t>Skipping never produces different numbers — only default ordering.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>If user select "just explore" - what's the next few screens they will see?</t>
-        </is>
-      </c>
+      <c r="G49" s="3" t="n"/>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -6529,11 +6495,7 @@
 Both doors are full-width ≥48pt buttons announced with their sub-lines ('Connect your first account, takes about 2 minutes, read-only'). Illustration marked decorative (skipped by screen readers). Preview list is a proper list for rotor navigation.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>"your whole picture in one place" - your whole picture not clear - may be your entire finance picture or some thing? Same for "the few things need you, in dollars" - not sure what you mean by in dollars?</t>
-        </is>
-      </c>
+      <c r="G53" s="3" t="n"/>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -6764,11 +6726,7 @@
 Masked values announce as 'hidden' (not 'bullet bullet bullet'). Eye announces 'Show balances' when hidden — labels already exist in src/components/TopBar.tsx. The banner is polite-priority for screen readers (announced once, not repeated per element).</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>This does not have refresh date and time.</t>
-        </is>
-      </c>
+      <c r="G62" s="3" t="n"/>
     </row>
     <row r="63" ht="46" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -6944,11 +6902,7 @@
 Banner is announced once on arrival ('Information: Chase hasn't updated since June 27'), not on every scroll. Stamps are part of each number's spoken sentence ('…as of June 27'). Info icon always paired with words. Fix button ≥44pt.</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>in mock up 1 - date and time was after "your investments" and before " Net Worth", here it is after "net worth". Which is the right place?</t>
-        </is>
-      </c>
+      <c r="G69" s="3" t="n"/>
     </row>
     <row r="70" ht="46" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -7145,11 +7099,7 @@
 Read as one story: fact, where, comparison. Rates always paired with the word estimate.</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>From where comparative data coming? Do we have analytical engine built to analyze all imported data and come up with these insights?</t>
-        </is>
-      </c>
+      <c r="G77" s="3" t="n"/>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
@@ -7361,6 +7311,7 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
     </row>
+    <row r="87"/>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
@@ -7601,11 +7552,7 @@
 Every row is a button whose spoken label includes name, amount, source and last-updated ('Fidelity Brokerage, $521,300, connected, updated today 6:04 am'). Own/owe conveyed by section words and minus signs, never color alone; paused connections say 'paused' in text. All targets at least 44 points; text scales with system size; the trend line carries a one-sentence spoken summary.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Double check in strategy and design document - did we say that people think in terms of non-retirement and retirement accounts? If yes, do we want to list retirement account as Retirement account (401K/IRA/etc.). We should have info dots for all asset classes. </t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -7633,11 +7580,7 @@
           <t>The exact number shown on Home and everywhere else — every surface calls buildNetWorth(totalAssets, totalDebtBalance); pinned by the cross-screen agreement test (src/domain/assets/agreement.test.ts).</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Plain line - means line graph?</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7773,11 +7716,7 @@
           <t>The stamp describes freshness only; the amount itself is always the stored balance that totalAssets sums — stale never means different.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>what does screen look like for manual update?</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -7832,11 +7771,7 @@
           <t>All three paths write accounts through the same store.addAsset / store.updateAsset actions (src/store/useStore.ts), so a linked, imported, or hand-typed account is the same kind of row everywhere.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Review the Add account screen to make sure it we have separate screen or dynamic screen adjusting by asset class ensuring we are collecting right and required information. </t>
-        </is>
-      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -7891,11 +7826,7 @@
           <t>cashTotal is the same canonical cash number as the Cash row above it; plannedMonthlySpend is the same budget figure the Plan tab uses.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Cash = cash + cash equivalent?</t>
-        </is>
-      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -7923,11 +7854,7 @@
           <t>PIN: identical projection to Plan's will-it-last detail band and Invest's forward what-if baseline — one engine, one assumptions source; TODAY's balances never move on adoption (futures only).</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>is the display graph, table, or just numbers?</t>
-        </is>
-      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -8057,11 +7984,7 @@
 Consent card is real text (not an image), scales with system size, and is read in full by the screen reader before the Continue button. Buttons are labeled with outcomes ('Continue to Plaid to sign in to Fidelity, read-only'). Progress states are announced. Color never carries meaning alone.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>import from a file - do we need specific format if yes, we should specify. May be have a info dot to explain file type and must have columns?</t>
-        </is>
-      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20" ht="46" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -8317,11 +8240,7 @@
           <t>Linked accounts enter the same accounts array every total reads — totalAssets, assetAllocation and buildNetWorth pick them up with zero new math.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>do we capture only balance or all individual portfolio holding e.g. AMZN 100 stocks ….</t>
-        </is>
-      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -8730,11 +8649,7 @@
 Action buttons say their outcome ('Record a deposit into Chase Checking'). History rows read as full sentences with signed amounts spoken as 'minus five thousand two hundred dollars'. The stale-value nudge is a labeled alert, and the paused state is announced in words. All amounts respect hidden-balances in spoken output too.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>When dividend is captured is it automatically added to income or cash? Similarly, is there a way captical gain is captured and displayed somewhere?</t>
-        </is>
-      </c>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -8965,11 +8880,7 @@
 Every field labeled; the maturity picker announces the chosen date (existing accessibility label kept). The 12-month cash-vs-bond rule is stated in visible text under the date, not hidden in a tooltip. Sale confirmations read the full sentence including both values. Nudges are announced alerts.</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Is it imported directly using Plaid? Also, Does it capture interest payment for bonds? </t>
-        </is>
-      </c>
+      <c r="G54" s="3" t="n"/>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -9227,11 +9138,7 @@
 Chips are toggle buttons with selected state announced. Hints are visible text, not tooltips. Sale/close confirmations read as full sentences with both values. The staleness nudge is an announced alert paired with the clock icon and words.</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Is this manual, imported or connected and captured via Plaid? </t>
-        </is>
-      </c>
+      <c r="G64" s="3" t="n"/>
     </row>
     <row r="65" ht="46" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -9361,6 +9268,7 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
     </row>
+    <row r="70"/>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
@@ -9669,11 +9577,7 @@
 Gains/losses always carry the word 'up'/'down' plus an arrow icon — never red/green alone (colorblind-safe). Every row is one tap target 44pt+ with a spoken label like 'NVIDIA, $261,900, up 41 percent this year'. Period selector is a radio group announced as 'showing 1 year'. The trend chart has a text summary ('you +12.9%, market +10.1%') so screen readers don't need the picture.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Total return captures both realized and unrealized gains? Is there any place we display realized P/L, unrealized P/L, total dividend, and total interest separately?</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -9917,11 +9821,7 @@
           <t>The group subtotals and $843,700 total are the same balances Net Worth shows — recomputeBalances (src/store/useStore.ts:13) is the single writer of balance; pinned by the assets agreement test (src/domain/assets/agreement.test.ts).</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Is this expandable / collapasable as many people can have 20-30 or more holdings?</t>
-        </is>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -9976,11 +9876,7 @@
           <t>n/a (navigation)</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>What's the objective of "what if" - evaluate what if I had bought Nvidia instead of Amazon 6 months ago or something different?</t>
-        </is>
-      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -10008,11 +9904,7 @@
           <t>PIN: equals the Plan hub's committed saving and the Cash flow planned line — one shared source (F11).</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>How do we evaluate if something is saved towards retirement or some other goals? In other words is NW = Retire or Retire = Assets - Primary home - primary car?</t>
-        </is>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16" ht="64" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -10164,11 +10056,7 @@
 Header spoken as one sentence: 'NVIDIA, worth $261,900, up $76,200, 41 percent since purchase'. 'Ahead by 30.9 points' uses the word 'ahead', not color. Estimate labels are real text, not just styling, so screen readers hear them.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>stocks with dividends - will it also show dividends received?</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -11386,11 +11274,7 @@
 Type chips are a radio group. Guardrail messages are polite live-region announcements ('This buy costs more than the cash available'). History rows read as full sentences including the date.</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>If an account is connected but someone adds transaction manually - is that allowed and how will the reconciliation between captured info from Plaid versus manual entry happen?</t>
-        </is>
-      </c>
+      <c r="G69" s="3" t="n"/>
     </row>
     <row r="70" ht="46" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -12206,11 +12090,7 @@
 Surplus announced with direction words ('one thousand seven hundred forty dollars ahead'). Projection card is announced with its estimate disclaimer first. Bars carry full per-month spoken values.</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>What's the flow to add actual day to day expenses such grocery, gas, etc? Also, what's the flow to capture or add income?</t>
-        </is>
-      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -13588,11 +13468,7 @@
 Chance always pairs the percent with a word (Likely / Uncertain / Unlikely) so color never carries meaning alone. Band chart has a text alternative ('in the worst 1-in-10 futures, 71%'). All rows are one full-width tap target, minimum 44 points tall. Screen-reader order: headline, decisions, scenarios, revert, sharpen.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>"will it last" should it specify that this is about retirement? Right now it is not clear - what will last, and till when?</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -13774,6 +13650,7 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
@@ -13899,11 +13776,7 @@
           <t>PIN: the '67' row always equals the statement amount exactly (the factor at full claiming age is 1.0) -- a unit test pins this so the table can never drift from the user's own input.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>How is the amount calculated by age? Is this a formula used by social security administration?</t>
-        </is>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.1-2026-07-06.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.1-2026-07-06.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,8 +81,16 @@
       <b val="1"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6E43"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +112,11 @@
         <fgColor rgb="FFE7F3EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -117,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -155,6 +168,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -522,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -531,84 +550,91 @@
     <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>🔨 Build status · 2026-07-14 (Build #41 · v1.1.0 on TestFlight) — the whole-design build is ~85% shipped and on your phone. Per-screen status: new column on the Screen inventory tab; per-engine: New engines tab. Working status board: FCC-build-tracker.md · your walk sheet: docs/finwise-device-test-build41.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="140" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>✅ Approve?</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>💬 Your comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="140" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>WHAT CHANGED v1.0 → v1.1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Your v1.0 review (2026-07-06) = 32 in-document comments + 4 macro items. Every one is answered on the 'v1.0 review → v1.1' tab. Changes in this version: 3 NEW screens (Onboarding flow map · Add/edit an account by hand · Quick-add expense) — 40 screens total; 'Will my money last? — to age 92' naming everywhere; source-first income lines ('Social Security $2,600'); icon+color+word direction marks; info dots (investments/market/net worth definitions, asset classes, cash-equivalents, import file format, SSA formula, retirement earmark); 'Where the return came from' breakdown (realized · dividends · interest · on-paper — net-new); multi-select intents + what-FinWise-can-do intro; freshness stamp on every variant incl. hidden; retirement/non-retirement grouping; holdings-level sync + manual-transaction dedup rules; collapsible holdings groups; PROPOSED: top-bar '+' quick add replaces the net-worth chip (your approve/reject on the review tab). Keyboard rule (buttons never hide behind the keyboard) is now a gate in the UX doc.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>WHAT CHANGED v1.0 → v1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Your v1.0 review (2026-07-06) = 32 in-document comments + 4 macro items. Every one is answered on the 'v1.0 review → v1.1' tab. Changes in this version: 3 NEW screens (Onboarding flow map · Add/edit an account by hand · Quick-add expense) — 40 screens total; 'Will my money last? — to age 92' naming everywhere; source-first income lines ('Social Security $2,600'); icon+color+word direction marks; info dots (investments/market/net worth definitions, asset classes, cash-equivalents, import file format, SSA formula, retirement earmark); 'Where the return came from' breakdown (realized · dividends · interest · on-paper — net-new); multi-select intents + what-FinWise-can-do intro; freshness stamp on every variant incl. hidden; retirement/non-retirement grouping; holdings-level sync + manual-transaction dedup rules; collapsible holdings groups; PROPOSED: top-bar '+' quick add replaces the net-worth chip (your approve/reject on the review tab). Keyboard rule (buttons never hide behind the keyboard) is now a gate in the UX doc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="84" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>WHAT THIS IS</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>The DETAILED design for the FinWise 55-70 core: every screen of the five tabs (Home · Net worth · Invest · Cash flow · Plan), drawn as a phone wireframe with real example numbers, specified element by element — what each element shows, WHERE ITS NUMBER COMES FROM (the exact engine in the code, or the named net-new engine), which other screens must show the identical number, and every state (empty, loading, stale, hidden-balances, error).
 It implements the approved high-level design v1.2 and PRD v1.1 — including every change from your v1.0 review (activity recording for all asset classes, dated rolling months with the year visible, bond/alternative value freshness + rate-sensitivity estimate, institution capture on import, and 'Use this plan' adoption that updates the whole app).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="84" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HOW TO READ A SCREEN</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Each tab sheet lists its screens. Per screen: the WIREFRAME (a phone sketch — labels and numbers are realistic examples, not final copy), the PURPOSE, then an ELEMENT TABLE: element → what it shows (plain English) → data lineage (existing code helper, or NET-NEW engine) → the fields it reads → its sameness pin (which other screens must agree). Then STATES, interactions, accessibility notes, and a build note (reuse vs net-new). Mark Approve?/Comments on any screen row.</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="84" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BY THE NUMBERS</t>
+          <t>HOW TO READ A SCREEN</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>37 screens/variants across 5 tabs · 94 data-lineage rows (every on-screen number traced to its one engine) · 13 net-new engine specs (safe-to-spend paycheck, account-sync seam, dated canonical grid, scenario composer + adoption contract, multi-goal weigher, scam flag, bond rate-sensitivity).</t>
+          <t>Each tab sheet lists its screens. Per screen: the WIREFRAME (a phone sketch — labels and numbers are realistic examples, not final copy), the PURPOSE, then an ELEMENT TABLE: element → what it shows (plain English) → data lineage (existing code helper, or NET-NEW engine) → the fields it reads → its sameness pin (which other screens must agree). Then STATES, interactions, accessibility notes, and a build note (reuse vs net-new). Mark Approve?/Comments on any screen row.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>BY THE NUMBERS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>37 screens/variants across 5 tabs · 94 data-lineage rows (every on-screen number traced to its one engine) · 13 net-new engine specs (safe-to-spend paycheck, account-sync seam, dated canonical grid, scenario composer + adoption contract, multi-goal weigher, scam flag, bond rate-sensitivity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>WHAT COMES NEXT</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>You review this + PRD v1.1 + the UX design together. On approval: build, module by module, reusing the canonical helpers and extending the cross-screen agreement-test pattern to every new engine (one concept → one engine → one number).</t>
         </is>
@@ -3842,7 +3868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3852,6 +3878,7 @@
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3890,6 +3917,11 @@
           <t>💬 Your comments</t>
         </is>
       </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>🔨 Build status · 2026-07-14 (Build #41 · v1.1.0 on TestFlight)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -3919,6 +3951,11 @@
       </c>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — investments hero + what-needs-you + will-it-last; Home=Invest pin tested</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3948,6 +3985,11 @@
       </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — the paycheck leads, no flag; upgrade-from-#40 persona tested</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -3977,6 +4019,11 @@
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — engine + detail + slot-1 card; scam/fraud/alert copy test-banned</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -4006,6 +4053,11 @@
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/first-run + Settings → Your setup); insertion into new-user onboarding pending</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -4035,6 +4087,11 @@
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — honest empty state live; the FCC two-door layout pending</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -4064,6 +4121,11 @@
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — the zero-$ mask walk is an automated test</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -4093,6 +4155,11 @@
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — price freshness live; connection banner waits on the bank-connect build</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -4122,6 +4189,11 @@
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/idle-cash) — nudge repointed, dead-end closed</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -4151,6 +4223,11 @@
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — contribution-room screen + the try-it what-if prefill link</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -4180,6 +4257,11 @@
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — live under the new tab; rows now open Account detail; FCC glance re-shell pending</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -4209,6 +4291,11 @@
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — bank connection sequenced last (sandbox keys live)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -4238,6 +4325,11 @@
       </c>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — the never-double merge rule IS built and shared with Import v2</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -4267,6 +4359,11 @@
       </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — institution required, update-not-twin merge, correctable classes</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -4296,6 +4393,11 @@
       </c>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/account-detail) — per-class activity through the one ledger; freshness nudge</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -4325,6 +4427,11 @@
       </c>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (pre-existing, kept)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -4354,6 +4461,11 @@
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (pre-existing, kept)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -4383,6 +4495,11 @@
       </c>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — glance header + Home pin done; drill re-shell pending</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -4412,6 +4529,11 @@
       </c>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — per-holding returns show inline on the Invest table meanwhile</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -4441,6 +4563,11 @@
       </c>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — facts + yields + the rates-move estimate, on Account detail</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -4470,6 +4597,11 @@
       </c>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — typical return + reported return + look-back door, on Account detail</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -4499,6 +4631,11 @@
       </c>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/look-back) — real past prices only; design example pinned to the dollar</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -4528,6 +4665,11 @@
       </c>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/what-if) — before-chance = hub chance, pinned; prefill wired</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -4557,6 +4699,11 @@
       </c>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (pre-existing, kept)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -4586,6 +4733,11 @@
       </c>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — mask + freshness pinned by tests; the written state contract pending</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -4615,6 +4767,11 @@
       </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — hero + dated bars + draw-order preview + will-it-last strip</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -4644,6 +4801,11 @@
       </c>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — in/out/surplus + commitments seam + the projection card</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -4673,6 +4835,11 @@
       </c>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/month-detail) — pure cell renderer; rows-sum pin tested</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -4702,6 +4869,11 @@
       </c>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — v1 calendar linked everywhere; running-balance table pending</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -4731,6 +4903,11 @@
       </c>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — order preview + the Why sheet live; steering pending</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -4760,6 +4937,11 @@
       </c>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — the retired fast-path door</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -4789,6 +4971,11 @@
       </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — band, decisions, scenarios, revert, sharpen meter</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -4818,6 +5005,11 @@
       </c>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/ss-timing) — SSA table pinned to the design dollars; adoption + revert tested</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -4847,6 +5039,11 @@
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/multi-goal) — verdict vs canonical capacity; commitments named on Cash flow</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -4876,6 +5073,11 @@
       </c>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — existing calculator linked from the hub; scenario adoption pending</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -4905,6 +5107,11 @@
       </c>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — rmd-due insight + hub row land on the cockpit; dedicated screen pending</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -4934,6 +5141,11 @@
       </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — the shared adoption sheet; one write path, always revertible</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -4963,6 +5175,11 @@
       </c>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built (/will-it-last) — sourced drivers, one-selector headline pinned</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -4992,6 +5209,11 @@
       </c>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — existing onboarding carries new users meanwhile</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -5021,6 +5243,11 @@
       </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — the existing AssetSheet editor remains</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -5050,6 +5277,11 @@
       </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — the '+ Expense' button + shared sheet on Home and Cash flow</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7311,7 +7543,6 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
     </row>
-    <row r="87"/>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
@@ -9268,7 +9499,6 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
     </row>
-    <row r="70"/>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
@@ -12011,7 +12241,6 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -12274,7 +12503,6 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -12500,7 +12728,6 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="46" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
@@ -12787,7 +13014,6 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -13014,7 +13240,6 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
@@ -13185,7 +13410,6 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
     </row>
-    <row r="60"/>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
@@ -13650,7 +13874,6 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
@@ -15147,7 +15370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15155,6 +15378,7 @@
     <col width="108" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -15181,6 +15405,11 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>💬 Your comments</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>🔨 Build status · 2026-07-14 (Build #41 · v1.1.0 on TestFlight)</t>
         </is>
       </c>
     </row>
@@ -15234,6 +15463,11 @@
 GUARANTEED — EXACT DEFINITION (added at strategy-trace review; prevents double counting): guaranteed = ri_ss + ri_pension + ri_annuities + ri_other, received-now only. ri_withdrawals and ri_rmd are EXCLUDED from guaranteed income — the solved safe draw and the pinned required withdrawal REPLACE them, so a savings-draw is never counted twice in the paycheck. The B-31 snapshot pin (snapshot.guaranteed_monthly_income) aligns to this definition. NOTED v1 BOUNDARIES (strategy trace): a big purchase's effect on WHICH account gets tapped shows only via the steer-sheet re-run; overspend-vs-paycheck tracking is scenario-path only ('try it in Plan') — both named boundaries, phase-2 candidates.</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built + projection mode (the working-lens future-paycheck card)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="400" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -15280,6 +15514,11 @@
 3) Real placement: one test walks a bonus (chosen month), a vest (its months), a one-time item (its real date), an annual pension (its month), and a deferred debt (its first payment month) through Home, Cash flow, Bill calendar, Month detail, and Plan — same month everywhere, by construction and by test.</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — every by-month surface reads its cells</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="196" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -15303,6 +15542,11 @@
 6) STATES CARRIED BY THE ENGINE: sandbox banner text ('this won't change your plan until you tap Use this plan') is supplied by useScenario() so every scenario screen says it identically; post-adoption confirmation re-reads the store (proof the write landed) rather than trusting the sheet's memory.</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>✅ Core built — adoptPlan/revertPlan/planHistory + the shared sheet</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="196" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -15324,6 +15568,11 @@
 4) WILL-IT-LAST HOOK. Retirement effect uses the EXISTING engines, never a parallel formula: chance via simulate() (src/domain/retirement/index.ts:115) and retire age via solveRetireAge (:225), both fed with the retirement dial (times 12) as the contribution and everything else from the shared assumptions object. Before/after panel: 'before' = current adopted plan through selectWillItLast (so it always equals the hub); 'after' = the sandbox combination. Trim-one hints re-run the same math with one dial reduced a standard step (e.g. to 60%) -- deterministic because simulate() is seeded -- and are worded descriptively ('Parents at $1,500: retire 68, chance 81%'), never as advice; tapping a hint just moves that slider.
 5) ADOPTION. 'Use this plan' hands F11 the patch {contribMonthly = retirement dial, commitments = toggled rows with label, monthlyAmount, endDate}. Downstream per the propagation map: each commitment appears as a named planned monthly line in Cash flow's F5 paycheck view; the hub's will-it-last and Home's hero pick up the new chance; Net worth's projection band reflects the new contribution path. Nothing moves real money; goals' recorded progress is untouched.
 6) TESTS THAT PIN IT: capacity equals Cash flow's available-to-save (cross-screen agreement); single-goal finish dates match the standalone goal math; the before-side of every before/after equals the hub headline; trim-hint numbers reproduce exactly when the slider is set to the hint's amount; adopt-then-revert restores the pre-adoption composer state.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — weighGoals + trim hints as pre-runs (pinned identical)</t>
         </is>
       </c>
     </row>
@@ -15351,6 +15600,11 @@
 ADDED AT ROUND-2 REVIEW: (1) HOLDINGS-LEVEL SYNC (c20/c22): investment accounts sync positions (shares per holding) and investment transactions — including bond positions and interest/coupon payments where the institution reports them (ledger types INTEREST/COUPON exist); bank accounts sync balances + transactions. (2) MANUAL TRANSACTIONS ON CONNECTED ACCOUNTS (c29): allowed but guarded — a hand-added transaction is tagged 'entered by you'; when the connection later delivers a match (same amount, ±3 days, similar description) the app asks once 'Same transaction?' and merges on yes. Balances defer to the connection's truth on next sync, so a double entry can never permanently distort the balance.</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — sequenced last; Transaction.source + merge rule ready</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="140" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -15372,6 +15626,11 @@
 SAMENESS: the Cash flow tab, Account detail history, and every balance all read the same ledger and the same engine; recording from any screen produces the identical result, pinned by the existing transactions tests (src/domain/transactions/transactions.test.ts) plus new ones for the bond/alternative paths.</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — per-class recording through the one engine on Account detail</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="84" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -15391,6 +15650,11 @@
 ALL THREE are small, unit-testable extensions of existing code (holdingsImport.test.ts already covers the parser), not a rebuild.</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — institution + provenance + merge-not-duplicate</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -15408,6 +15672,11 @@
           <t>WHAT IT IS: a small always-on check that looks at each new money-out transaction and, when one stands out, puts a calm 'Worth a look' card on Home — a fact plus two buttons, never an alarm. INPUTS: every new transaction where money leaves an account (types WITHDRAWAL, TRANSFER to an account we don't recognize as yours, or FEE) from the existing transaction record (fields used: date, type, account, amount, payee text in the note); plus that same account's last 90 days of money-out history. THE RULES (any one trips a flag; checked in this order): (1) UNUSUALLY LARGE — the amount is at least 3 times that account's typical money-out (the middle value of the last 90 days' withdrawals) AND at least $500; if the account has fewer than 5 past withdrawals to learn from, use a flat $1,000 line instead. (2) FIRST-TIME PAYEE — the payee text has never appeared on this account before AND the amount is at least $250. (3) ODD PATTERN — 3 or more money-out transactions from the same account within one calendar day adding to $1,000 or more (shown as one combined card). OUTPUT: a flag saved alongside the transaction: which transaction, which account, which rule fired, the comparison figure the rule used (e.g. 'typical is $310' — stored at flag time so the explanation never drifts), the dollar amount, a status (open / this-was-me / flagged-by-you), and timestamps. WHAT THE PERSON SEES: at most ONE card on Home at a time (the most recent, with 'and 1 more' if others are open), wording always 'Worth a look' with a magnifying-glass icon — the words scam, fraud, and alert never appear in version 1, and the card is never red. RESOLUTION: 'Yes, this was me' closes it (and for a first-time payee, remembers that payee so it never asks again); 'Something's off' shows a short factual checklist (call the number on the back of your bank card; change any recently shared codes) and keeps a quiet follow-up on Home until marked settled. LEARNING: only the known-payee memory; thresholds are fixed in v1 — no automatic tightening or loosening. HARD LIMITS: we only read; we never block, move, or report anything — the copy says so on the card's detail view. NEW FIELDS: flag record (flag_id, transaction_id, account_id, reason, comparison, amount, status, created_at, resolved_at) and a per-account known-payee list. Proposed home: src/domain/transactions/flags.ts as a pure function reviewTransactions(newOnes, history) → flags, unit-testable with no app plumbing. MANUAL-ENTRY RULE (added after the retired-persona walkthrough): transactions the user typed by hand are NEVER flagged — you don't interrogate someone about a number they just told you. The watch runs on connected-account transactions only, and the design says so honestly: users with no connected accounts see a one-time quiet note on the transaction history ('When you connect an account, we watch it for odd transactions — hand-typed entries are yours, we never question them') instead of a permanently silent feature that looks broken. Copy consistency: the 'Something's off' checklist says 'call the number on the back of your bank card' — the word 'fraud' stays banned in v1 copy everywhere, including the checklist.</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — 3 fixed rules; manual rows never flagged</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -15423,6 +15692,11 @@
       <c r="C10" s="3" t="inlineStr">
         <is>
           <t>WHAT IT IS: the small record that lets Home be honest about old data. Each linked institution gets a Connection record: institution name, when it last updated successfully, and a status (fine / needs your login again). RULES: the Home banner appears when any connection is more than 48 hours old or needs a fresh login, naming the institution and the date, with one Fix button that re-links only that institution; people who only added things by hand never see it. Every number that includes data from a stale connection carries an 'as of &lt;date&gt;' stamp (balances: oldest included connection date — NET-NEW; prices: the existing priceFreshness helper in src/services/marketData.ts, reused unchanged). Settings' connections list reads the SAME records, so the banner and Settings can never disagree. This rides on the F1 account-sync seam (no aggregator module exists in the repo yet); the price-staleness stamps can ship before F1 does. FIELDS: Connection {institution, last_successful_update, status} plus a link from each synced account to its connection.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>🔨 Partial — value_as_of freshness live; connection records wait on F1</t>
         </is>
       </c>
     </row>
@@ -15448,6 +15722,11 @@
 LABELING: card title carries 'Estimate, not a prediction'; the info dot explains the method in two sentences; values say 'roughly'. Colorblind-safe: 'down/up' words + arrows, never color alone. Test pins: monotonic (higher rate -&gt; lower value), reproduces the example above within the stated range, hidden-state cases return null.</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — surfaced on the bond detail card</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="168" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -15470,6 +15749,11 @@
 LABELING: fixed caption 'Real past prices; not a prediction of what happens next.' Never phrased as 'you should have' — wording is 'it became / it would be'. Test pins: each path's % equals periodReturn for the same ticker/window; cash path returns the amount unchanged; insufficient-history returns a refusal, not a number.</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — real prices only, never extrapolated</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="140" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -15491,6 +15775,11 @@
 LABELING: factual and calm ('Still about right?'), never alarmist; dismiss rests the nudge for another 6 months. Test pins: stale flips at exactly 6 months; keep-it re-stamps without touching balance; Net Worth agreement unaffected (balance unchanged by stamping).</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>✅ Built — the 6-month 'still right?' nudge</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="112" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -15511,6 +15800,11 @@
 WORDING RULES: percent + the word 'one stock/one account' + the name; never 'too much', never 'consider selling'. When both holding-level and account-level fire, show the holding-level one (more specific) — never two callouts. Test pins: threshold constants referenced from one place; the callout % equals the same holding's listed share; suppressed below threshold and when total priced value is zero. PEER FRAMING (the 36-65 strategy and high-level v1.2 C2 asked for 'more than most people your age'): explicitly DEFERRED in v1 — there is no honest peer-benchmark data source; shipping the phrase without one would be an invented fact. Recorded as a decision, not an omission; phase-2 candidate with a sourced benchmark.</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Not built — the account-level concentration insight ships meanwhile</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
